--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168828</v>
+        <v>120168831</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513319</v>
+        <v>513185</v>
       </c>
       <c r="R2" t="n">
-        <v>7088030</v>
+        <v>7088034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168831</v>
+        <v>120168815</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513185</v>
+        <v>513222</v>
       </c>
       <c r="R3" t="n">
-        <v>7088034</v>
+        <v>7087903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168825</v>
+        <v>120168824</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513428</v>
+        <v>513469</v>
       </c>
       <c r="R4" t="n">
-        <v>7087959</v>
+        <v>7087930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168812</v>
+        <v>120168819</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513333</v>
+        <v>513413</v>
       </c>
       <c r="R5" t="n">
-        <v>7088018</v>
+        <v>7087803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168846</v>
+        <v>120168825</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513511</v>
+        <v>513428</v>
       </c>
       <c r="R6" t="n">
-        <v>7087876</v>
+        <v>7087959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168818</v>
+        <v>120168833</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513379</v>
+        <v>513139</v>
       </c>
       <c r="R7" t="n">
-        <v>7087839</v>
+        <v>7088009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168815</v>
+        <v>120168827</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513222</v>
+        <v>513324</v>
       </c>
       <c r="R8" t="n">
-        <v>7087903</v>
+        <v>7088028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168824</v>
+        <v>120168826</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513469</v>
+        <v>513337</v>
       </c>
       <c r="R9" t="n">
-        <v>7087930</v>
+        <v>7087981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168833</v>
+        <v>120168816</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1561,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513139</v>
+        <v>513263</v>
       </c>
       <c r="R10" t="n">
-        <v>7088009</v>
+        <v>7087831</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168826</v>
+        <v>120168828</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513337</v>
+        <v>513319</v>
       </c>
       <c r="R11" t="n">
-        <v>7087981</v>
+        <v>7088030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168820</v>
+        <v>120168830</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1775,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513434</v>
+        <v>513249</v>
       </c>
       <c r="R12" t="n">
-        <v>7087819</v>
+        <v>7088026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168819</v>
+        <v>120168846</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513413</v>
+        <v>513511</v>
       </c>
       <c r="R13" t="n">
-        <v>7087803</v>
+        <v>7087876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168843</v>
+        <v>120168812</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513282</v>
+        <v>513333</v>
       </c>
       <c r="R14" t="n">
-        <v>7087879</v>
+        <v>7088018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168829</v>
+        <v>120168820</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513255</v>
+        <v>513434</v>
       </c>
       <c r="R15" t="n">
-        <v>7088026</v>
+        <v>7087819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168814</v>
+        <v>120168843</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513195</v>
+        <v>513282</v>
       </c>
       <c r="R16" t="n">
-        <v>7087852</v>
+        <v>7087879</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168816</v>
+        <v>120168814</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513263</v>
+        <v>513195</v>
       </c>
       <c r="R18" t="n">
-        <v>7087831</v>
+        <v>7087852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168830</v>
+        <v>120168823</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513249</v>
+        <v>513471</v>
       </c>
       <c r="R19" t="n">
-        <v>7088026</v>
+        <v>7087919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168817</v>
+        <v>120168818</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513321</v>
+        <v>513379</v>
       </c>
       <c r="R20" t="n">
-        <v>7087837</v>
+        <v>7087839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168827</v>
+        <v>120168829</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513324</v>
+        <v>513255</v>
       </c>
       <c r="R21" t="n">
-        <v>7088028</v>
+        <v>7088026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168823</v>
+        <v>120168817</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513471</v>
+        <v>513321</v>
       </c>
       <c r="R23" t="n">
-        <v>7087919</v>
+        <v>7087837</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168831</v>
+        <v>120168846</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513185</v>
+        <v>513511</v>
       </c>
       <c r="R2" t="n">
-        <v>7088034</v>
+        <v>7087876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168815</v>
+        <v>120168824</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513222</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>7087903</v>
+        <v>7087930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168824</v>
+        <v>120168818</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513469</v>
+        <v>513379</v>
       </c>
       <c r="R4" t="n">
-        <v>7087930</v>
+        <v>7087839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168819</v>
+        <v>120168817</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513413</v>
+        <v>513321</v>
       </c>
       <c r="R5" t="n">
-        <v>7087803</v>
+        <v>7087837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168825</v>
+        <v>120168826</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513428</v>
+        <v>513337</v>
       </c>
       <c r="R6" t="n">
-        <v>7087959</v>
+        <v>7087981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168833</v>
+        <v>120168823</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513139</v>
+        <v>513471</v>
       </c>
       <c r="R7" t="n">
-        <v>7088009</v>
+        <v>7087919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168827</v>
+        <v>120168815</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513324</v>
+        <v>513222</v>
       </c>
       <c r="R8" t="n">
-        <v>7088028</v>
+        <v>7087903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168826</v>
+        <v>120168822</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513337</v>
+        <v>513514</v>
       </c>
       <c r="R9" t="n">
-        <v>7087981</v>
+        <v>7087862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168816</v>
+        <v>120168825</v>
       </c>
       <c r="B10" t="n">
         <v>57310</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513263</v>
+        <v>513428</v>
       </c>
       <c r="R10" t="n">
-        <v>7087831</v>
+        <v>7087959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168828</v>
+        <v>120168843</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,16 +1649,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513319</v>
+        <v>513282</v>
       </c>
       <c r="R11" t="n">
-        <v>7088030</v>
+        <v>7087879</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168846</v>
+        <v>120168827</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513511</v>
+        <v>513324</v>
       </c>
       <c r="R13" t="n">
-        <v>7087876</v>
+        <v>7088028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168820</v>
+        <v>120168829</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513434</v>
+        <v>513255</v>
       </c>
       <c r="R15" t="n">
-        <v>7087819</v>
+        <v>7088026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168843</v>
+        <v>120168819</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513282</v>
+        <v>513413</v>
       </c>
       <c r="R16" t="n">
-        <v>7087879</v>
+        <v>7087803</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168822</v>
+        <v>120168820</v>
       </c>
       <c r="B17" t="n">
         <v>57310</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513514</v>
+        <v>513434</v>
       </c>
       <c r="R17" t="n">
-        <v>7087862</v>
+        <v>7087819</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168814</v>
+        <v>120168833</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513195</v>
+        <v>513139</v>
       </c>
       <c r="R18" t="n">
-        <v>7087852</v>
+        <v>7088009</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168823</v>
+        <v>120168831</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513471</v>
+        <v>513185</v>
       </c>
       <c r="R19" t="n">
-        <v>7087919</v>
+        <v>7088034</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168818</v>
+        <v>120168832</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513379</v>
+        <v>513141</v>
       </c>
       <c r="R20" t="n">
-        <v>7087839</v>
+        <v>7088010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168829</v>
+        <v>120168828</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513255</v>
+        <v>513319</v>
       </c>
       <c r="R21" t="n">
-        <v>7088026</v>
+        <v>7088030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168832</v>
+        <v>120168816</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513141</v>
+        <v>513263</v>
       </c>
       <c r="R22" t="n">
-        <v>7088010</v>
+        <v>7087831</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168817</v>
+        <v>120168814</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513321</v>
+        <v>513195</v>
       </c>
       <c r="R23" t="n">
-        <v>7087837</v>
+        <v>7087852</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168826</v>
+        <v>120168823</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513337</v>
+        <v>513471</v>
       </c>
       <c r="R6" t="n">
-        <v>7087981</v>
+        <v>7087919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168823</v>
+        <v>120168826</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513471</v>
+        <v>513337</v>
       </c>
       <c r="R7" t="n">
-        <v>7087919</v>
+        <v>7087981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168823</v>
+        <v>120168826</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513471</v>
+        <v>513337</v>
       </c>
       <c r="R6" t="n">
-        <v>7087919</v>
+        <v>7087981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168826</v>
+        <v>120168823</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513337</v>
+        <v>513471</v>
       </c>
       <c r="R7" t="n">
-        <v>7087981</v>
+        <v>7087919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168824</v>
+        <v>120168818</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513469</v>
+        <v>513379</v>
       </c>
       <c r="R3" t="n">
-        <v>7087930</v>
+        <v>7087839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168818</v>
+        <v>120168824</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513379</v>
+        <v>513469</v>
       </c>
       <c r="R4" t="n">
-        <v>7087839</v>
+        <v>7087930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168846</v>
+        <v>120168816</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513511</v>
+        <v>513263</v>
       </c>
       <c r="R2" t="n">
-        <v>7087876</v>
+        <v>7087831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168818</v>
+        <v>120168826</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513379</v>
+        <v>513337</v>
       </c>
       <c r="R3" t="n">
-        <v>7087839</v>
+        <v>7087981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168824</v>
+        <v>120168830</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513469</v>
+        <v>513249</v>
       </c>
       <c r="R4" t="n">
-        <v>7087930</v>
+        <v>7088026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168817</v>
+        <v>120168832</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513321</v>
+        <v>513141</v>
       </c>
       <c r="R5" t="n">
-        <v>7087837</v>
+        <v>7088010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168823</v>
+        <v>120168814</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513471</v>
+        <v>513195</v>
       </c>
       <c r="R6" t="n">
-        <v>7087919</v>
+        <v>7087852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168826</v>
+        <v>120168846</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513337</v>
+        <v>513511</v>
       </c>
       <c r="R7" t="n">
-        <v>7087981</v>
+        <v>7087876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168815</v>
+        <v>120168812</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513222</v>
+        <v>513333</v>
       </c>
       <c r="R8" t="n">
-        <v>7087903</v>
+        <v>7088018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168822</v>
+        <v>120168824</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513514</v>
+        <v>513469</v>
       </c>
       <c r="R9" t="n">
-        <v>7087862</v>
+        <v>7087930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168825</v>
+        <v>120168827</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513428</v>
+        <v>513324</v>
       </c>
       <c r="R10" t="n">
-        <v>7087959</v>
+        <v>7088028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168843</v>
+        <v>120168819</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,16 +1644,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513282</v>
+        <v>513413</v>
       </c>
       <c r="R11" t="n">
-        <v>7087879</v>
+        <v>7087803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168830</v>
+        <v>120168829</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,7 +1775,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513249</v>
+        <v>513255</v>
       </c>
       <c r="R12" t="n">
         <v>7088026</v>
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168827</v>
+        <v>120168825</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513324</v>
+        <v>513428</v>
       </c>
       <c r="R13" t="n">
-        <v>7088028</v>
+        <v>7087959</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168812</v>
+        <v>120168843</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513333</v>
+        <v>513282</v>
       </c>
       <c r="R14" t="n">
-        <v>7088018</v>
+        <v>7087879</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168829</v>
+        <v>120168815</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513255</v>
+        <v>513222</v>
       </c>
       <c r="R15" t="n">
-        <v>7088026</v>
+        <v>7087903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168819</v>
+        <v>120168817</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513413</v>
+        <v>513321</v>
       </c>
       <c r="R16" t="n">
-        <v>7087803</v>
+        <v>7087837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168820</v>
+        <v>120168831</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513434</v>
+        <v>513185</v>
       </c>
       <c r="R17" t="n">
-        <v>7087819</v>
+        <v>7088034</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,7 +2380,7 @@
         <v>120168833</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168831</v>
+        <v>120168822</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513185</v>
+        <v>513514</v>
       </c>
       <c r="R19" t="n">
-        <v>7088034</v>
+        <v>7087862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168832</v>
+        <v>120168828</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513141</v>
+        <v>513319</v>
       </c>
       <c r="R20" t="n">
-        <v>7088010</v>
+        <v>7088030</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168828</v>
+        <v>120168820</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513319</v>
+        <v>513434</v>
       </c>
       <c r="R21" t="n">
-        <v>7088030</v>
+        <v>7087819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168816</v>
+        <v>120168818</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513263</v>
+        <v>513379</v>
       </c>
       <c r="R22" t="n">
-        <v>7087831</v>
+        <v>7087839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168814</v>
+        <v>120168823</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513195</v>
+        <v>513471</v>
       </c>
       <c r="R23" t="n">
-        <v>7087852</v>
+        <v>7087919</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168846</v>
+        <v>120168824</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513511</v>
+        <v>513469</v>
       </c>
       <c r="R7" t="n">
-        <v>7087876</v>
+        <v>7087930</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168812</v>
+        <v>120168827</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513333</v>
+        <v>513324</v>
       </c>
       <c r="R8" t="n">
-        <v>7088018</v>
+        <v>7088028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168824</v>
+        <v>120168812</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513469</v>
+        <v>513333</v>
       </c>
       <c r="R9" t="n">
-        <v>7087930</v>
+        <v>7088018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168827</v>
+        <v>120168846</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513324</v>
+        <v>513511</v>
       </c>
       <c r="R10" t="n">
-        <v>7088028</v>
+        <v>7087876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168816</v>
+        <v>120168828</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513263</v>
+        <v>513319</v>
       </c>
       <c r="R2" t="n">
-        <v>7087831</v>
+        <v>7088030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168826</v>
+        <v>120168833</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513337</v>
+        <v>513139</v>
       </c>
       <c r="R3" t="n">
-        <v>7087981</v>
+        <v>7088009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168830</v>
+        <v>120168829</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513249</v>
+        <v>513255</v>
       </c>
       <c r="R4" t="n">
         <v>7088026</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168832</v>
+        <v>120168846</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513141</v>
+        <v>513511</v>
       </c>
       <c r="R5" t="n">
-        <v>7088010</v>
+        <v>7087876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168814</v>
+        <v>120168822</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513195</v>
+        <v>513514</v>
       </c>
       <c r="R6" t="n">
-        <v>7087852</v>
+        <v>7087862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168824</v>
+        <v>120168843</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513469</v>
+        <v>513282</v>
       </c>
       <c r="R7" t="n">
-        <v>7087930</v>
+        <v>7087879</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168827</v>
+        <v>120168830</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513324</v>
+        <v>513249</v>
       </c>
       <c r="R8" t="n">
-        <v>7088028</v>
+        <v>7088026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168812</v>
+        <v>120168832</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513333</v>
+        <v>513141</v>
       </c>
       <c r="R9" t="n">
-        <v>7088018</v>
+        <v>7088010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168846</v>
+        <v>120168815</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513511</v>
+        <v>513222</v>
       </c>
       <c r="R10" t="n">
-        <v>7087876</v>
+        <v>7087903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168819</v>
+        <v>120168823</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513413</v>
+        <v>513471</v>
       </c>
       <c r="R11" t="n">
-        <v>7087803</v>
+        <v>7087919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168829</v>
+        <v>120168827</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513255</v>
+        <v>513324</v>
       </c>
       <c r="R12" t="n">
-        <v>7088026</v>
+        <v>7088028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168825</v>
+        <v>120168820</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513428</v>
+        <v>513434</v>
       </c>
       <c r="R13" t="n">
-        <v>7087959</v>
+        <v>7087819</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168843</v>
+        <v>120168825</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1970,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513282</v>
+        <v>513428</v>
       </c>
       <c r="R14" t="n">
-        <v>7087879</v>
+        <v>7087959</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168815</v>
+        <v>120168831</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513222</v>
+        <v>513185</v>
       </c>
       <c r="R15" t="n">
-        <v>7087903</v>
+        <v>7088034</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168817</v>
+        <v>120168826</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513321</v>
+        <v>513337</v>
       </c>
       <c r="R16" t="n">
-        <v>7087837</v>
+        <v>7087981</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168831</v>
+        <v>120168818</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513185</v>
+        <v>513379</v>
       </c>
       <c r="R17" t="n">
-        <v>7088034</v>
+        <v>7087839</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168833</v>
+        <v>120168817</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513139</v>
+        <v>513321</v>
       </c>
       <c r="R18" t="n">
-        <v>7088009</v>
+        <v>7087837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168822</v>
+        <v>120168819</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513514</v>
+        <v>513413</v>
       </c>
       <c r="R19" t="n">
-        <v>7087862</v>
+        <v>7087803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168828</v>
+        <v>120168812</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513319</v>
+        <v>513333</v>
       </c>
       <c r="R20" t="n">
-        <v>7088030</v>
+        <v>7088018</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2672,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168820</v>
+        <v>120168816</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513434</v>
+        <v>513263</v>
       </c>
       <c r="R21" t="n">
-        <v>7087819</v>
+        <v>7087831</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168818</v>
+        <v>120168814</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513379</v>
+        <v>513195</v>
       </c>
       <c r="R22" t="n">
-        <v>7087839</v>
+        <v>7087852</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168823</v>
+        <v>120168824</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513471</v>
+        <v>513469</v>
       </c>
       <c r="R23" t="n">
-        <v>7087919</v>
+        <v>7087930</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168828</v>
+        <v>120168843</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513319</v>
+        <v>513282</v>
       </c>
       <c r="R2" t="n">
-        <v>7088030</v>
+        <v>7087879</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168833</v>
+        <v>120168819</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513139</v>
+        <v>513413</v>
       </c>
       <c r="R3" t="n">
-        <v>7088009</v>
+        <v>7087803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168829</v>
+        <v>120168833</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513255</v>
+        <v>513139</v>
       </c>
       <c r="R4" t="n">
-        <v>7088026</v>
+        <v>7088009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168822</v>
+        <v>120168830</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513514</v>
+        <v>513249</v>
       </c>
       <c r="R6" t="n">
-        <v>7087862</v>
+        <v>7088026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168843</v>
+        <v>120168829</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513282</v>
+        <v>513255</v>
       </c>
       <c r="R7" t="n">
-        <v>7087879</v>
+        <v>7088026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168830</v>
+        <v>120168831</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513249</v>
+        <v>513185</v>
       </c>
       <c r="R8" t="n">
-        <v>7088026</v>
+        <v>7088034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168832</v>
+        <v>120168818</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513141</v>
+        <v>513379</v>
       </c>
       <c r="R9" t="n">
-        <v>7088010</v>
+        <v>7087839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168815</v>
+        <v>120168817</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513222</v>
+        <v>513321</v>
       </c>
       <c r="R10" t="n">
-        <v>7087903</v>
+        <v>7087837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168823</v>
+        <v>120168827</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513471</v>
+        <v>513324</v>
       </c>
       <c r="R11" t="n">
-        <v>7087919</v>
+        <v>7088028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168827</v>
+        <v>120168832</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513324</v>
+        <v>513141</v>
       </c>
       <c r="R12" t="n">
-        <v>7088028</v>
+        <v>7088010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168820</v>
+        <v>120168816</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513434</v>
+        <v>513263</v>
       </c>
       <c r="R13" t="n">
-        <v>7087819</v>
+        <v>7087831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168825</v>
+        <v>120168814</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513428</v>
+        <v>513195</v>
       </c>
       <c r="R14" t="n">
-        <v>7087959</v>
+        <v>7087852</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168831</v>
+        <v>120168828</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513185</v>
+        <v>513319</v>
       </c>
       <c r="R15" t="n">
-        <v>7088034</v>
+        <v>7088030</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168826</v>
+        <v>120168822</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513337</v>
+        <v>513514</v>
       </c>
       <c r="R16" t="n">
-        <v>7087981</v>
+        <v>7087862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168818</v>
+        <v>120168825</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513379</v>
+        <v>513428</v>
       </c>
       <c r="R17" t="n">
-        <v>7087839</v>
+        <v>7087959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168817</v>
+        <v>120168815</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513321</v>
+        <v>513222</v>
       </c>
       <c r="R18" t="n">
-        <v>7087837</v>
+        <v>7087903</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168819</v>
+        <v>120168823</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513413</v>
+        <v>513471</v>
       </c>
       <c r="R19" t="n">
-        <v>7087803</v>
+        <v>7087919</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168816</v>
+        <v>120168820</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513263</v>
+        <v>513434</v>
       </c>
       <c r="R21" t="n">
-        <v>7087831</v>
+        <v>7087819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168814</v>
+        <v>120168824</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513195</v>
+        <v>513469</v>
       </c>
       <c r="R22" t="n">
-        <v>7087852</v>
+        <v>7087930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168824</v>
+        <v>120168826</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513469</v>
+        <v>513337</v>
       </c>
       <c r="R23" t="n">
-        <v>7087930</v>
+        <v>7087981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168832</v>
+        <v>120168816</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513141</v>
+        <v>513263</v>
       </c>
       <c r="R12" t="n">
-        <v>7088010</v>
+        <v>7087831</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168816</v>
+        <v>120168832</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513263</v>
+        <v>513141</v>
       </c>
       <c r="R13" t="n">
-        <v>7087831</v>
+        <v>7088010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168843</v>
+        <v>120168817</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513282</v>
+        <v>513321</v>
       </c>
       <c r="R2" t="n">
-        <v>7087879</v>
+        <v>7087837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168819</v>
+        <v>120168824</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513413</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>7087803</v>
+        <v>7087930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168833</v>
+        <v>120168826</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513139</v>
+        <v>513337</v>
       </c>
       <c r="R4" t="n">
-        <v>7088009</v>
+        <v>7087981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168846</v>
+        <v>120168820</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513511</v>
+        <v>513434</v>
       </c>
       <c r="R5" t="n">
-        <v>7087876</v>
+        <v>7087819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168830</v>
+        <v>120168846</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513249</v>
+        <v>513511</v>
       </c>
       <c r="R6" t="n">
-        <v>7088026</v>
+        <v>7087876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168829</v>
+        <v>120168825</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513255</v>
+        <v>513428</v>
       </c>
       <c r="R7" t="n">
-        <v>7088026</v>
+        <v>7087959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168831</v>
+        <v>120168843</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513185</v>
+        <v>513282</v>
       </c>
       <c r="R8" t="n">
-        <v>7088034</v>
+        <v>7087879</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168818</v>
+        <v>120168812</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513379</v>
+        <v>513333</v>
       </c>
       <c r="R9" t="n">
-        <v>7087839</v>
+        <v>7088018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168817</v>
+        <v>120168829</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513321</v>
+        <v>513255</v>
       </c>
       <c r="R10" t="n">
-        <v>7087837</v>
+        <v>7088026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168827</v>
+        <v>120168816</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513324</v>
+        <v>513263</v>
       </c>
       <c r="R11" t="n">
-        <v>7088028</v>
+        <v>7087831</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168816</v>
+        <v>120168818</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513263</v>
+        <v>513379</v>
       </c>
       <c r="R12" t="n">
-        <v>7087831</v>
+        <v>7087839</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168832</v>
+        <v>120168819</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513141</v>
+        <v>513413</v>
       </c>
       <c r="R13" t="n">
-        <v>7088010</v>
+        <v>7087803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168814</v>
+        <v>120168827</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513195</v>
+        <v>513324</v>
       </c>
       <c r="R14" t="n">
-        <v>7087852</v>
+        <v>7088028</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168828</v>
+        <v>120168832</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513319</v>
+        <v>513141</v>
       </c>
       <c r="R15" t="n">
-        <v>7088030</v>
+        <v>7088010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168822</v>
+        <v>120168814</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513514</v>
+        <v>513195</v>
       </c>
       <c r="R16" t="n">
-        <v>7087862</v>
+        <v>7087852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168825</v>
+        <v>120168830</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513428</v>
+        <v>513249</v>
       </c>
       <c r="R17" t="n">
-        <v>7087959</v>
+        <v>7088026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168815</v>
+        <v>120168828</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513222</v>
+        <v>513319</v>
       </c>
       <c r="R18" t="n">
-        <v>7087903</v>
+        <v>7088030</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168823</v>
+        <v>120168833</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513471</v>
+        <v>513139</v>
       </c>
       <c r="R19" t="n">
-        <v>7087919</v>
+        <v>7088009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168812</v>
+        <v>120168815</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513333</v>
+        <v>513222</v>
       </c>
       <c r="R20" t="n">
-        <v>7088018</v>
+        <v>7087903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168820</v>
+        <v>120168831</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513434</v>
+        <v>513185</v>
       </c>
       <c r="R21" t="n">
-        <v>7087819</v>
+        <v>7088034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168824</v>
+        <v>120168822</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513469</v>
+        <v>513514</v>
       </c>
       <c r="R22" t="n">
-        <v>7087930</v>
+        <v>7087862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168826</v>
+        <v>120168823</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513337</v>
+        <v>513471</v>
       </c>
       <c r="R23" t="n">
-        <v>7087981</v>
+        <v>7087919</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168817</v>
+        <v>120168823</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513321</v>
+        <v>513471</v>
       </c>
       <c r="R2" t="n">
-        <v>7087837</v>
+        <v>7087919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168824</v>
+        <v>120168828</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513469</v>
+        <v>513319</v>
       </c>
       <c r="R3" t="n">
-        <v>7087930</v>
+        <v>7088030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168826</v>
+        <v>120168831</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513337</v>
+        <v>513185</v>
       </c>
       <c r="R4" t="n">
-        <v>7087981</v>
+        <v>7088034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168820</v>
+        <v>120168822</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513434</v>
+        <v>513514</v>
       </c>
       <c r="R5" t="n">
-        <v>7087819</v>
+        <v>7087862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168846</v>
+        <v>120168816</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513511</v>
+        <v>513263</v>
       </c>
       <c r="R6" t="n">
-        <v>7087876</v>
+        <v>7087831</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168825</v>
+        <v>120168815</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513428</v>
+        <v>513222</v>
       </c>
       <c r="R7" t="n">
-        <v>7087959</v>
+        <v>7087903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168843</v>
+        <v>120168830</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513282</v>
+        <v>513249</v>
       </c>
       <c r="R8" t="n">
-        <v>7087879</v>
+        <v>7088026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168812</v>
+        <v>120168825</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513333</v>
+        <v>513428</v>
       </c>
       <c r="R9" t="n">
-        <v>7088018</v>
+        <v>7087959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168829</v>
+        <v>120168817</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1561,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513255</v>
+        <v>513321</v>
       </c>
       <c r="R10" t="n">
-        <v>7088026</v>
+        <v>7087837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168816</v>
+        <v>120168819</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513263</v>
+        <v>513413</v>
       </c>
       <c r="R11" t="n">
-        <v>7087831</v>
+        <v>7087803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168818</v>
+        <v>120168824</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1775,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513379</v>
+        <v>513469</v>
       </c>
       <c r="R12" t="n">
-        <v>7087839</v>
+        <v>7087930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168819</v>
+        <v>120168846</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513413</v>
+        <v>513511</v>
       </c>
       <c r="R13" t="n">
-        <v>7087803</v>
+        <v>7087876</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168827</v>
+        <v>120168826</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513324</v>
+        <v>513337</v>
       </c>
       <c r="R14" t="n">
-        <v>7088028</v>
+        <v>7087981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168814</v>
+        <v>120168818</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513195</v>
+        <v>513379</v>
       </c>
       <c r="R16" t="n">
-        <v>7087852</v>
+        <v>7087839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168830</v>
+        <v>120168843</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,16 +2291,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513249</v>
+        <v>513282</v>
       </c>
       <c r="R17" t="n">
-        <v>7088026</v>
+        <v>7087879</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168828</v>
+        <v>120168829</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513319</v>
+        <v>513255</v>
       </c>
       <c r="R18" t="n">
-        <v>7088030</v>
+        <v>7088026</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168833</v>
+        <v>120168812</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513139</v>
+        <v>513333</v>
       </c>
       <c r="R19" t="n">
-        <v>7088009</v>
+        <v>7088018</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2560,11 +2565,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2591,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168815</v>
+        <v>120168820</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513222</v>
+        <v>513434</v>
       </c>
       <c r="R20" t="n">
-        <v>7087903</v>
+        <v>7087819</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168831</v>
+        <v>120168814</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513185</v>
+        <v>513195</v>
       </c>
       <c r="R21" t="n">
-        <v>7088034</v>
+        <v>7087852</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168822</v>
+        <v>120168833</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513514</v>
+        <v>513139</v>
       </c>
       <c r="R22" t="n">
-        <v>7087862</v>
+        <v>7088009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168823</v>
+        <v>120168827</v>
       </c>
       <c r="B23" t="n">
         <v>57320</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513471</v>
+        <v>513324</v>
       </c>
       <c r="R23" t="n">
-        <v>7087919</v>
+        <v>7088028</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168823</v>
+        <v>120168816</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513471</v>
+        <v>513263</v>
       </c>
       <c r="R2" t="n">
-        <v>7087919</v>
+        <v>7087831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168828</v>
+        <v>120168820</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513319</v>
+        <v>513434</v>
       </c>
       <c r="R3" t="n">
-        <v>7088030</v>
+        <v>7087819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168831</v>
+        <v>120168843</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513185</v>
+        <v>513282</v>
       </c>
       <c r="R4" t="n">
-        <v>7088034</v>
+        <v>7087879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168822</v>
+        <v>120168832</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513514</v>
+        <v>513141</v>
       </c>
       <c r="R5" t="n">
-        <v>7087862</v>
+        <v>7088010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168816</v>
+        <v>120168814</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513263</v>
+        <v>513195</v>
       </c>
       <c r="R6" t="n">
-        <v>7087831</v>
+        <v>7087852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168815</v>
+        <v>120168826</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513222</v>
+        <v>513337</v>
       </c>
       <c r="R7" t="n">
-        <v>7087903</v>
+        <v>7087981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168830</v>
+        <v>120168831</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513249</v>
+        <v>513185</v>
       </c>
       <c r="R8" t="n">
-        <v>7088026</v>
+        <v>7088034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168825</v>
+        <v>120168817</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513428</v>
+        <v>513321</v>
       </c>
       <c r="R9" t="n">
-        <v>7087959</v>
+        <v>7087837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168817</v>
+        <v>120168815</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513321</v>
+        <v>513222</v>
       </c>
       <c r="R10" t="n">
-        <v>7087837</v>
+        <v>7087903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168819</v>
+        <v>120168824</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513413</v>
+        <v>513469</v>
       </c>
       <c r="R11" t="n">
-        <v>7087803</v>
+        <v>7087930</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168824</v>
+        <v>120168825</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513469</v>
+        <v>513428</v>
       </c>
       <c r="R12" t="n">
-        <v>7087930</v>
+        <v>7087959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168846</v>
+        <v>120168827</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513511</v>
+        <v>513324</v>
       </c>
       <c r="R13" t="n">
-        <v>7087876</v>
+        <v>7088028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1928,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168826</v>
+        <v>120168846</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513337</v>
+        <v>513511</v>
       </c>
       <c r="R14" t="n">
-        <v>7087981</v>
+        <v>7087876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,11 +2035,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168832</v>
+        <v>120168819</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513141</v>
+        <v>513413</v>
       </c>
       <c r="R15" t="n">
-        <v>7088010</v>
+        <v>7087803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168818</v>
+        <v>120168829</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513379</v>
+        <v>513255</v>
       </c>
       <c r="R16" t="n">
-        <v>7087839</v>
+        <v>7088026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120168843</v>
+        <v>120168833</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,16 +2291,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513282</v>
+        <v>513139</v>
       </c>
       <c r="R17" t="n">
-        <v>7087879</v>
+        <v>7088009</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168829</v>
+        <v>120168828</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513255</v>
+        <v>513319</v>
       </c>
       <c r="R18" t="n">
-        <v>7088026</v>
+        <v>7088030</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168812</v>
+        <v>120168830</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513333</v>
+        <v>513249</v>
       </c>
       <c r="R19" t="n">
-        <v>7088018</v>
+        <v>7088026</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,6 +2565,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168820</v>
+        <v>120168823</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513434</v>
+        <v>513471</v>
       </c>
       <c r="R20" t="n">
-        <v>7087819</v>
+        <v>7087919</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168814</v>
+        <v>120168822</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513195</v>
+        <v>513514</v>
       </c>
       <c r="R21" t="n">
-        <v>7087852</v>
+        <v>7087862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168833</v>
+        <v>120168818</v>
       </c>
       <c r="B22" t="n">
         <v>57320</v>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513139</v>
+        <v>513379</v>
       </c>
       <c r="R22" t="n">
-        <v>7088009</v>
+        <v>7087839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168827</v>
+        <v>120168812</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513324</v>
+        <v>513333</v>
       </c>
       <c r="R23" t="n">
-        <v>7088028</v>
+        <v>7088018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,11 +2993,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 58149-2023 artfynd.xlsx
+++ b/artfynd/A 58149-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120168816</v>
+        <v>120168820</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513263</v>
+        <v>513434</v>
       </c>
       <c r="R2" t="n">
-        <v>7087831</v>
+        <v>7087819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120168820</v>
+        <v>120168823</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513434</v>
+        <v>513471</v>
       </c>
       <c r="R3" t="n">
-        <v>7087819</v>
+        <v>7087919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack ganska färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120168843</v>
+        <v>120168815</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513282</v>
+        <v>513222</v>
       </c>
       <c r="R4" t="n">
-        <v>7087879</v>
+        <v>7087903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120168832</v>
+        <v>120168816</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513141</v>
+        <v>513263</v>
       </c>
       <c r="R5" t="n">
-        <v>7088010</v>
+        <v>7087831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120168814</v>
+        <v>120168831</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513195</v>
+        <v>513185</v>
       </c>
       <c r="R6" t="n">
-        <v>7087852</v>
+        <v>7088034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till något äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120168826</v>
+        <v>120168828</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513337</v>
+        <v>513319</v>
       </c>
       <c r="R7" t="n">
-        <v>7087981</v>
+        <v>7088030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120168831</v>
+        <v>120168814</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513185</v>
+        <v>513195</v>
       </c>
       <c r="R8" t="n">
-        <v>7088034</v>
+        <v>7087852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska till något äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120168817</v>
+        <v>120168824</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513321</v>
+        <v>513469</v>
       </c>
       <c r="R9" t="n">
-        <v>7087837</v>
+        <v>7087930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120168815</v>
+        <v>120168829</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513222</v>
+        <v>513255</v>
       </c>
       <c r="R10" t="n">
-        <v>7087903</v>
+        <v>7088026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120168824</v>
+        <v>120168825</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513469</v>
+        <v>513428</v>
       </c>
       <c r="R11" t="n">
-        <v>7087930</v>
+        <v>7087959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120168825</v>
+        <v>120168843</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513428</v>
+        <v>513282</v>
       </c>
       <c r="R12" t="n">
-        <v>7087959</v>
+        <v>7087879</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120168827</v>
+        <v>120168822</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513324</v>
+        <v>513514</v>
       </c>
       <c r="R13" t="n">
-        <v>7088028</v>
+        <v>7087862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120168846</v>
+        <v>120168812</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513511</v>
+        <v>513333</v>
       </c>
       <c r="R14" t="n">
-        <v>7087876</v>
+        <v>7088018</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120168819</v>
+        <v>120168830</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513413</v>
+        <v>513249</v>
       </c>
       <c r="R15" t="n">
-        <v>7087803</v>
+        <v>7088026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120168829</v>
+        <v>120168827</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513255</v>
+        <v>513324</v>
       </c>
       <c r="R16" t="n">
-        <v>7088026</v>
+        <v>7088028</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120168828</v>
+        <v>120168832</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513319</v>
+        <v>513141</v>
       </c>
       <c r="R18" t="n">
-        <v>7088030</v>
+        <v>7088010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120168830</v>
+        <v>120168818</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513249</v>
+        <v>513379</v>
       </c>
       <c r="R19" t="n">
-        <v>7088026</v>
+        <v>7087839</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120168823</v>
+        <v>120168817</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513471</v>
+        <v>513321</v>
       </c>
       <c r="R20" t="n">
-        <v>7087919</v>
+        <v>7087837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack ganska färska till äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120168822</v>
+        <v>120168826</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513514</v>
+        <v>513337</v>
       </c>
       <c r="R21" t="n">
-        <v>7087862</v>
+        <v>7087981</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120168818</v>
+        <v>120168846</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513379</v>
+        <v>513511</v>
       </c>
       <c r="R22" t="n">
-        <v>7087839</v>
+        <v>7087876</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,11 +2886,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120168812</v>
+        <v>120168819</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513333</v>
+        <v>513413</v>
       </c>
       <c r="R23" t="n">
-        <v>7088018</v>
+        <v>7087803</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,6 +2988,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
